--- a/excel/ALCOHOL.xlsx
+++ b/excel/ALCOHOL.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="630" yWindow="540" windowWidth="27495" windowHeight="13995"/>
+    <workbookView xWindow="630" yWindow="540" windowWidth="27495" windowHeight="13995" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Matching" sheetId="2" r:id="rId1"/>
